--- a/data/schools.xlsx
+++ b/data/schools.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid\Downloads\بيانات المدارس\بيانات المدارس\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid\AppData\Local\EditExcel\Sessions\BB0303897D6B9842BF4B3EAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="210">
   <si>
     <t>اسم المدرسة</t>
   </si>
@@ -646,6 +646,9 @@
   </si>
   <si>
     <t>https://maps.app.goo.gl/Fgmcb6q96A6XPxEh6</t>
+  </si>
+  <si>
+    <t>محمد علي كلاي</t>
   </si>
 </sst>
 </file>
@@ -1868,7 +1871,9 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A28" s="1"/>
+      <c r="A28" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="B28" s="1"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>

--- a/data/schools.xlsx
+++ b/data/schools.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="211">
   <si>
     <t>اسم المدرسة</t>
   </si>
@@ -649,6 +649,9 @@
   </si>
   <si>
     <t>محمد علي كلاي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">احمد يوسف كريم </t>
   </si>
 </sst>
 </file>
@@ -1885,7 +1888,9 @@
       <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A29" s="1"/>
+      <c r="A29" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="B29" s="1"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>

--- a/data/schools.xlsx
+++ b/data/schools.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="213">
   <si>
     <t>اسم المدرسة</t>
   </si>
@@ -652,6 +652,12 @@
   </si>
   <si>
     <t xml:space="preserve">احمد يوسف كريم </t>
+  </si>
+  <si>
+    <t xml:space="preserve">وليد عبدلله زيدان عبيد </t>
+  </si>
+  <si>
+    <t xml:space="preserve">كريم يوسف </t>
   </si>
 </sst>
 </file>
@@ -1902,7 +1908,9 @@
       <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A30" s="1"/>
+      <c r="A30" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="B30" s="1"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1914,7 +1922,9 @@
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A31" s="1"/>
+      <c r="A31" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="B31" s="1"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>

--- a/data/schools.xlsx
+++ b/data/schools.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="214">
   <si>
     <t>اسم المدرسة</t>
   </si>
@@ -658,6 +658,9 @@
   </si>
   <si>
     <t xml:space="preserve">كريم يوسف </t>
+  </si>
+  <si>
+    <t xml:space="preserve">شريفه محمد كريم </t>
   </si>
 </sst>
 </file>
@@ -1936,7 +1939,9 @@
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A32" s="1"/>
+      <c r="A32" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="B32" s="1"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>

--- a/data/schools.xlsx
+++ b/data/schools.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="215">
   <si>
     <t>اسم المدرسة</t>
   </si>
@@ -661,6 +661,9 @@
   </si>
   <si>
     <t xml:space="preserve">شريفه محمد كريم </t>
+  </si>
+  <si>
+    <t xml:space="preserve">هاجر سيد علي </t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1956,9 @@
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A33" s="1"/>
+      <c r="A33" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="B33" s="1"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>

--- a/data/schools.xlsx
+++ b/data/schools.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="216">
   <si>
     <t>اسم المدرسة</t>
   </si>
@@ -664,6 +664,9 @@
   </si>
   <si>
     <t xml:space="preserve">هاجر سيد علي </t>
+  </si>
+  <si>
+    <t xml:space="preserve">يوسف علي حسين </t>
   </si>
 </sst>
 </file>
@@ -1970,7 +1973,9 @@
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A34" s="1"/>
+      <c r="A34" s="1" t="s">
+        <v>215</v>
+      </c>
       <c r="B34" s="1"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>

--- a/data/schools.xlsx
+++ b/data/schools.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="217">
   <si>
     <t>اسم المدرسة</t>
   </si>
@@ -667,6 +667,9 @@
   </si>
   <si>
     <t xml:space="preserve">يوسف علي حسين </t>
+  </si>
+  <si>
+    <t>بابلابلابلابلابلا</t>
   </si>
 </sst>
 </file>
@@ -1987,7 +1990,9 @@
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A35" s="1"/>
+      <c r="A35" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="B35" s="1"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
